--- a/radious-new.xlsx
+++ b/radious-new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oggy\Downloads\temp-ctf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07DBB442-20B0-4175-B939-5DDC9B8BF34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85C39B4-1B28-45B1-A5A6-3581E09AA5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="304">
   <si>
     <t>Brand</t>
   </si>
@@ -246,9 +246,6 @@
   </si>
   <si>
     <t>Panasonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no </t>
   </si>
   <si>
     <t>Bertazzoni</t>
@@ -2795,7 +2792,7 @@
         <v>65</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D116" s="6"/>
     </row>
@@ -2807,7 +2804,7 @@
         <v>65</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D117" s="6"/>
     </row>
@@ -2819,7 +2816,7 @@
         <v>65</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D118" s="6"/>
     </row>
@@ -2831,7 +2828,7 @@
         <v>65</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D119" s="6"/>
     </row>
@@ -2843,7 +2840,7 @@
         <v>65</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D120" s="6"/>
     </row>
@@ -2855,7 +2852,7 @@
         <v>65</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D121" s="6"/>
     </row>
@@ -2867,7 +2864,7 @@
         <v>65</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D122" s="6"/>
     </row>
@@ -2879,7 +2876,7 @@
         <v>65</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D123" s="6"/>
     </row>
@@ -2891,7 +2888,7 @@
         <v>65</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D124" s="6"/>
     </row>
@@ -2903,7 +2900,7 @@
         <v>65</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D125" s="6"/>
     </row>
@@ -2915,7 +2912,7 @@
         <v>65</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D126" s="6"/>
       <c r="E126" s="11"/>
@@ -2949,7 +2946,7 @@
         <v>65</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D127" s="6"/>
     </row>
@@ -2961,7 +2958,7 @@
         <v>65</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D128" s="6"/>
     </row>
@@ -2973,7 +2970,7 @@
         <v>65</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D129" s="6"/>
     </row>
@@ -2985,7 +2982,7 @@
         <v>65</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D130" s="6"/>
     </row>
@@ -2997,7 +2994,7 @@
         <v>65</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D131" s="6"/>
     </row>
@@ -3009,7 +3006,7 @@
         <v>65</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D132" s="6"/>
     </row>
@@ -3021,7 +3018,7 @@
         <v>65</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D133" s="6"/>
     </row>
@@ -3033,7 +3030,7 @@
         <v>65</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D134" s="6"/>
     </row>
@@ -3045,7 +3042,7 @@
         <v>65</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D135" s="6"/>
     </row>
@@ -3057,7 +3054,7 @@
         <v>65</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D136" s="6"/>
     </row>
@@ -3069,7 +3066,7 @@
         <v>65</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D137" s="6"/>
     </row>
@@ -3081,7 +3078,7 @@
         <v>65</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D138" s="6"/>
     </row>
@@ -3093,7 +3090,7 @@
         <v>65</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D139" s="6"/>
     </row>
@@ -3105,7 +3102,7 @@
         <v>65</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D140" s="6"/>
       <c r="E140" s="7"/>
@@ -3119,7 +3116,7 @@
         <v>65</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="7"/>
@@ -3133,7 +3130,7 @@
         <v>65</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D142" s="6"/>
       <c r="E142" s="7"/>
@@ -3147,7 +3144,7 @@
         <v>65</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="7"/>
@@ -3155,13 +3152,13 @@
     </row>
     <row r="144" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>65</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D144" s="6"/>
       <c r="E144" s="7"/>
@@ -3175,7 +3172,7 @@
         <v>65</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D145" s="6"/>
       <c r="E145" s="7"/>
@@ -3189,7 +3186,7 @@
         <v>65</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D146" s="6"/>
       <c r="E146" s="7"/>
@@ -3203,7 +3200,7 @@
         <v>65</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D147" s="6"/>
       <c r="E147" s="7"/>
@@ -3217,7 +3214,7 @@
         <v>65</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D148" s="6"/>
     </row>
@@ -3229,7 +3226,7 @@
         <v>65</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D149" s="12"/>
     </row>
@@ -3241,7 +3238,7 @@
         <v>65</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D150" s="12"/>
     </row>
@@ -3253,7 +3250,7 @@
         <v>65</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D151" s="12"/>
     </row>
@@ -3265,7 +3262,7 @@
         <v>65</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D152" s="12"/>
     </row>
@@ -3277,7 +3274,7 @@
         <v>65</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D153" s="12"/>
     </row>
@@ -3289,7 +3286,7 @@
         <v>65</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D154" s="12"/>
     </row>
@@ -3301,7 +3298,7 @@
         <v>65</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D155" s="12"/>
     </row>
@@ -3313,7 +3310,7 @@
         <v>65</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D156" s="12"/>
     </row>
@@ -3325,31 +3322,31 @@
         <v>65</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D157" s="12"/>
     </row>
     <row r="158" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>65</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D158" s="12"/>
     </row>
     <row r="159" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>65</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D159" s="12"/>
     </row>
@@ -3361,7 +3358,7 @@
         <v>65</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D160" s="12"/>
     </row>
@@ -3373,7 +3370,7 @@
         <v>65</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D161" s="12"/>
       <c r="E161" s="7"/>
@@ -3386,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D162" s="12"/>
       <c r="E162" s="13"/>
@@ -3400,7 +3397,7 @@
         <v>65</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D163" s="12"/>
     </row>
@@ -3412,7 +3409,7 @@
         <v>65</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D164" s="12"/>
     </row>
@@ -3424,7 +3421,7 @@
         <v>65</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D165" s="12"/>
     </row>
@@ -3436,7 +3433,7 @@
         <v>65</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D166" s="12"/>
     </row>
@@ -3448,7 +3445,7 @@
         <v>65</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D167" s="12"/>
     </row>
@@ -3460,7 +3457,7 @@
         <v>65</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D168" s="12"/>
     </row>
@@ -3472,7 +3469,7 @@
         <v>65</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D169" s="12"/>
     </row>
@@ -3484,19 +3481,19 @@
         <v>65</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D170" s="12"/>
     </row>
     <row r="171" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>65</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D171" s="12"/>
     </row>
@@ -3508,7 +3505,7 @@
         <v>65</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D172" s="12"/>
     </row>
@@ -3517,10 +3514,10 @@
         <v>64</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D173" s="12"/>
     </row>
@@ -3529,10 +3526,10 @@
         <v>6</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D174" s="12"/>
     </row>
@@ -3541,10 +3538,10 @@
         <v>66</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D175" s="12"/>
     </row>
@@ -3553,10 +3550,10 @@
         <v>8</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3564,10 +3561,10 @@
         <v>9</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3575,10 +3572,10 @@
         <v>10</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3586,10 +3583,10 @@
         <v>67</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3597,10 +3594,10 @@
         <v>68</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3608,10 +3605,10 @@
         <v>13</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3619,10 +3616,10 @@
         <v>14</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3630,10 +3627,10 @@
         <v>15</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3641,10 +3638,10 @@
         <v>69</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3652,10 +3649,10 @@
         <v>17</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3663,10 +3660,10 @@
         <v>70</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3674,10 +3671,10 @@
         <v>19</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3685,10 +3682,10 @@
         <v>20</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3696,10 +3693,10 @@
         <v>71</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3707,10 +3704,10 @@
         <v>22</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3718,10 +3715,10 @@
         <v>72</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3729,10 +3726,10 @@
         <v>24</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3740,10 +3737,10 @@
         <v>25</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D193" s="15"/>
       <c r="E193" s="7"/>
@@ -3753,10 +3750,10 @@
         <v>26</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E194" s="7"/>
       <c r="F194" s="8"/>
@@ -3766,10 +3763,10 @@
         <v>27</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E195" s="7"/>
       <c r="F195" s="8"/>
@@ -3779,10 +3776,10 @@
         <v>28</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E196" s="7"/>
       <c r="F196" s="8"/>
@@ -3792,10 +3789,10 @@
         <v>29</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E197" s="7"/>
       <c r="F197" s="8"/>
@@ -3805,10 +3802,10 @@
         <v>30</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E198" s="7"/>
       <c r="F198" s="8"/>
@@ -3818,10 +3815,10 @@
         <v>31</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E199" s="7"/>
       <c r="F199" s="8"/>
@@ -3831,23 +3828,23 @@
         <v>33</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E200" s="7"/>
       <c r="F200" s="8"/>
     </row>
     <row r="201" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E201" s="7"/>
       <c r="F201" s="8"/>
@@ -3857,10 +3854,10 @@
         <v>35</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E202" s="7"/>
       <c r="F202" s="8"/>
@@ -3870,10 +3867,10 @@
         <v>36</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E203" s="7"/>
       <c r="F203" s="8"/>
@@ -3883,10 +3880,10 @@
         <v>37</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E204" s="7"/>
       <c r="F204" s="8"/>
@@ -3896,10 +3893,10 @@
         <v>38</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E205" s="7"/>
       <c r="F205" s="8"/>
@@ -3909,10 +3906,10 @@
         <v>39</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E206" s="7"/>
       <c r="F206" s="8"/>
@@ -3922,10 +3919,10 @@
         <v>40</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E207" s="7"/>
       <c r="F207" s="8"/>
@@ -3935,10 +3932,10 @@
         <v>41</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E208" s="7"/>
       <c r="F208" s="8"/>
@@ -3948,10 +3945,10 @@
         <v>42</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="210" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3959,10 +3956,10 @@
         <v>43</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3970,10 +3967,10 @@
         <v>44</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3981,10 +3978,10 @@
         <v>45</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3992,10 +3989,10 @@
         <v>46</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4003,32 +4000,32 @@
         <v>47</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="217" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4036,10 +4033,10 @@
         <v>50</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="218" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4047,10 +4044,10 @@
         <v>51</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4058,10 +4055,10 @@
         <v>52</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="220" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4069,10 +4066,10 @@
         <v>53</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="221" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4080,10 +4077,10 @@
         <v>54</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4091,10 +4088,10 @@
         <v>55</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="223" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4102,10 +4099,10 @@
         <v>56</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="224" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4113,10 +4110,10 @@
         <v>57</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E224" s="7"/>
       <c r="F224" s="8"/>
@@ -4126,10 +4123,10 @@
         <v>58</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E225" s="7"/>
       <c r="F225" s="8"/>
@@ -4139,10 +4136,10 @@
         <v>59</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E226" s="7"/>
       <c r="F226" s="8"/>
@@ -4152,23 +4149,23 @@
         <v>60</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E227" s="7"/>
       <c r="F227" s="8"/>
     </row>
     <row r="228" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B228" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B228" s="5" t="s">
-        <v>78</v>
-      </c>
       <c r="C228" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E228" s="7"/>
       <c r="F228" s="8"/>
@@ -4178,10 +4175,10 @@
         <v>62</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E229" s="7"/>
       <c r="F229" s="8"/>
@@ -4191,10 +4188,10 @@
         <v>64</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E230" s="7"/>
       <c r="F230" s="8"/>
@@ -4204,10 +4201,10 @@
         <v>6</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="8"/>
@@ -4217,10 +4214,10 @@
         <v>66</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E232" s="7"/>
       <c r="F232" s="8"/>
@@ -4230,10 +4227,10 @@
         <v>8</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="8"/>
@@ -4243,10 +4240,10 @@
         <v>9</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E234" s="7"/>
       <c r="F234" s="8"/>
@@ -4256,10 +4253,10 @@
         <v>10</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E235" s="7"/>
       <c r="F235" s="8"/>
@@ -4269,10 +4266,10 @@
         <v>67</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E236" s="7"/>
       <c r="F236" s="8"/>
@@ -4282,10 +4279,10 @@
         <v>68</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="8"/>
@@ -4295,10 +4292,10 @@
         <v>13</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E238" s="7"/>
       <c r="F238" s="8"/>
@@ -4308,10 +4305,10 @@
         <v>14</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E239" s="7"/>
       <c r="F239" s="8"/>
@@ -4321,10 +4318,10 @@
         <v>15</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E240" s="7"/>
       <c r="F240" s="8"/>
@@ -4334,10 +4331,10 @@
         <v>69</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4345,10 +4342,10 @@
         <v>17</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4356,10 +4353,10 @@
         <v>70</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4367,10 +4364,10 @@
         <v>19</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4378,10 +4375,10 @@
         <v>20</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4389,10 +4386,10 @@
         <v>71</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4400,10 +4397,10 @@
         <v>22</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4411,10 +4408,10 @@
         <v>72</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4422,10 +4419,10 @@
         <v>24</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4433,10 +4430,10 @@
         <v>25</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4444,10 +4441,10 @@
         <v>26</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4455,10 +4452,10 @@
         <v>27</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4466,10 +4463,10 @@
         <v>28</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4477,10 +4474,10 @@
         <v>29</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4488,10 +4485,10 @@
         <v>30</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4499,10 +4496,10 @@
         <v>31</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="257" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4510,21 +4507,21 @@
         <v>33</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="258" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D258" s="15"/>
       <c r="E258" s="7"/>
@@ -4534,10 +4531,10 @@
         <v>35</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D259" s="15"/>
       <c r="E259" s="7"/>
@@ -4547,10 +4544,10 @@
         <v>36</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D260" s="15"/>
       <c r="E260" s="7"/>
@@ -4560,10 +4557,10 @@
         <v>37</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D261" s="15"/>
       <c r="E261" s="7"/>
@@ -4573,10 +4570,10 @@
         <v>38</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E262" s="7"/>
       <c r="F262" s="8"/>
@@ -4586,10 +4583,10 @@
         <v>39</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E263" s="7"/>
       <c r="F263" s="8"/>
@@ -4599,10 +4596,10 @@
         <v>40</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E264" s="7"/>
       <c r="F264" s="8"/>
@@ -4612,10 +4609,10 @@
         <v>41</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E265" s="7"/>
       <c r="F265" s="8"/>
@@ -4625,10 +4622,10 @@
         <v>42</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E266" s="7"/>
       <c r="F266" s="8"/>
@@ -4638,10 +4635,10 @@
         <v>43</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E267" s="7"/>
       <c r="F267" s="8"/>
@@ -4651,10 +4648,10 @@
         <v>44</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E268" s="7"/>
       <c r="F268" s="8"/>
@@ -4664,10 +4661,10 @@
         <v>45</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E269" s="7"/>
       <c r="F269" s="8"/>
@@ -4677,10 +4674,10 @@
         <v>46</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E270" s="7"/>
       <c r="F270" s="8"/>
@@ -4690,36 +4687,36 @@
         <v>47</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E271" s="7"/>
       <c r="F271" s="8"/>
     </row>
     <row r="272" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E272" s="7"/>
       <c r="F272" s="8"/>
     </row>
     <row r="273" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E273" s="7"/>
       <c r="F273" s="8"/>
@@ -4729,10 +4726,10 @@
         <v>50</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="275" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4740,10 +4737,10 @@
         <v>51</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="276" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4751,10 +4748,10 @@
         <v>52</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="277" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4762,10 +4759,10 @@
         <v>53</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="278" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4773,10 +4770,10 @@
         <v>54</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="279" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4784,10 +4781,10 @@
         <v>55</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="280" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4795,10 +4792,10 @@
         <v>56</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="281" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4806,10 +4803,10 @@
         <v>57</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="282" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4817,10 +4814,10 @@
         <v>58</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="283" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4828,10 +4825,10 @@
         <v>59</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="284" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4839,21 +4836,21 @@
         <v>60</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="285" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="286" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4861,10 +4858,10 @@
         <v>62</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D286" s="15"/>
     </row>
@@ -4873,7 +4870,7 @@
         <v>64</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C287" s="5" t="s">
         <v>32</v>
@@ -4885,7 +4882,7 @@
         <v>6</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C288" s="5" t="s">
         <v>32</v>
@@ -4897,10 +4894,10 @@
         <v>66</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E289" s="7"/>
     </row>
@@ -4909,10 +4906,10 @@
         <v>8</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E290" s="7"/>
     </row>
@@ -4921,7 +4918,7 @@
         <v>9</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C291" s="5" t="s">
         <v>32</v>
@@ -4933,10 +4930,10 @@
         <v>10</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E292" s="7"/>
     </row>
@@ -4945,10 +4942,10 @@
         <v>67</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E293" s="7"/>
     </row>
@@ -4957,7 +4954,7 @@
         <v>68</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C294" s="5" t="s">
         <v>32</v>
@@ -4969,7 +4966,7 @@
         <v>13</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C295" s="5" t="s">
         <v>32</v>
@@ -4981,10 +4978,10 @@
         <v>14</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E296" s="7"/>
     </row>
@@ -4993,7 +4990,7 @@
         <v>15</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C297" s="5" t="s">
         <v>32</v>
@@ -5005,7 +5002,7 @@
         <v>69</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C298" s="5" t="s">
         <v>32</v>
@@ -5017,7 +5014,7 @@
         <v>17</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C299" s="5" t="s">
         <v>32</v>
@@ -5029,10 +5026,10 @@
         <v>70</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E300" s="7"/>
     </row>
@@ -5041,7 +5038,7 @@
         <v>19</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C301" s="5" t="s">
         <v>32</v>
@@ -5053,7 +5050,7 @@
         <v>20</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C302" s="5" t="s">
         <v>32</v>
@@ -5065,10 +5062,10 @@
         <v>71</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E303" s="7"/>
     </row>
@@ -5077,7 +5074,7 @@
         <v>22</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C304" s="5" t="s">
         <v>32</v>
@@ -5089,7 +5086,7 @@
         <v>72</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C305" s="5" t="s">
         <v>32</v>
@@ -5101,7 +5098,7 @@
         <v>24</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C306" s="5" t="s">
         <v>32</v>
@@ -5113,10 +5110,10 @@
         <v>25</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E307" s="7"/>
     </row>
@@ -5125,7 +5122,7 @@
         <v>26</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C308" s="5" t="s">
         <v>32</v>
@@ -5137,7 +5134,7 @@
         <v>27</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C309" s="5" t="s">
         <v>32</v>
@@ -5149,7 +5146,7 @@
         <v>28</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C310" s="5" t="s">
         <v>32</v>
@@ -5161,7 +5158,7 @@
         <v>29</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C311" s="5" t="s">
         <v>32</v>
@@ -5173,10 +5170,10 @@
         <v>30</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D312" s="15"/>
     </row>
@@ -5185,7 +5182,7 @@
         <v>31</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C313" s="5" t="s">
         <v>32</v>
@@ -5197,7 +5194,7 @@
         <v>33</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C314" s="5" t="s">
         <v>32</v>
@@ -5206,10 +5203,10 @@
     </row>
     <row r="315" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C315" s="5" t="s">
         <v>32</v>
@@ -5221,7 +5218,7 @@
         <v>35</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C316" s="5" t="s">
         <v>32</v>
@@ -5233,7 +5230,7 @@
         <v>36</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C317" s="5" t="s">
         <v>32</v>
@@ -5245,7 +5242,7 @@
         <v>37</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C318" s="5" t="s">
         <v>32</v>
@@ -5257,7 +5254,7 @@
         <v>38</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C319" s="5" t="s">
         <v>32</v>
@@ -5269,7 +5266,7 @@
         <v>39</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C320" s="5" t="s">
         <v>32</v>
@@ -5281,7 +5278,7 @@
         <v>40</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C321" s="5" t="s">
         <v>32</v>
@@ -5293,7 +5290,7 @@
         <v>41</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C322" s="5" t="s">
         <v>32</v>
@@ -5305,7 +5302,7 @@
         <v>42</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C323" s="5" t="s">
         <v>32</v>
@@ -5317,7 +5314,7 @@
         <v>43</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C324" s="5" t="s">
         <v>32</v>
@@ -5329,7 +5326,7 @@
         <v>44</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C325" s="5" t="s">
         <v>32</v>
@@ -5341,7 +5338,7 @@
         <v>45</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C326" s="5" t="s">
         <v>32</v>
@@ -5353,7 +5350,7 @@
         <v>46</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C327" s="5" t="s">
         <v>32</v>
@@ -5365,7 +5362,7 @@
         <v>47</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C328" s="5" t="s">
         <v>32</v>
@@ -5374,10 +5371,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C329" s="5" t="s">
         <v>32</v>
@@ -5386,10 +5383,10 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C330" s="5" t="s">
         <v>32</v>
@@ -5401,7 +5398,7 @@
         <v>50</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C331" s="5" t="s">
         <v>32</v>
@@ -5413,7 +5410,7 @@
         <v>51</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C332" s="5" t="s">
         <v>32</v>
@@ -5425,7 +5422,7 @@
         <v>52</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C333" s="5" t="s">
         <v>32</v>
@@ -5437,7 +5434,7 @@
         <v>53</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C334" s="5" t="s">
         <v>32</v>
@@ -5449,7 +5446,7 @@
         <v>54</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C335" s="5" t="s">
         <v>32</v>
@@ -5461,7 +5458,7 @@
         <v>55</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C336" s="5" t="s">
         <v>32</v>
@@ -5473,7 +5470,7 @@
         <v>56</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C337" s="5" t="s">
         <v>32</v>
@@ -5485,7 +5482,7 @@
         <v>57</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C338" s="5" t="s">
         <v>32</v>
@@ -5497,7 +5494,7 @@
         <v>58</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C339" s="5" t="s">
         <v>32</v>
@@ -5509,7 +5506,7 @@
         <v>59</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C340" s="5" t="s">
         <v>32</v>
@@ -5521,7 +5518,7 @@
         <v>60</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C341" s="5" t="s">
         <v>32</v>
@@ -5530,10 +5527,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C342" s="5" t="s">
         <v>32</v>
@@ -5545,7 +5542,7 @@
         <v>62</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C343" s="5" t="s">
         <v>32</v>
@@ -10292,13 +10289,13 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="16" t="s">
         <v>82</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10306,10 +10303,10 @@
         <v>60002</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>84</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10317,10 +10314,10 @@
         <v>60004</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10328,10 +10325,10 @@
         <v>60005</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10339,10 +10336,10 @@
         <v>60006</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10350,10 +10347,10 @@
         <v>60007</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E6" s="7"/>
     </row>
@@ -10362,10 +10359,10 @@
         <v>60008</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10373,10 +10370,10 @@
         <v>60009</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10384,10 +10381,10 @@
         <v>60010</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10395,10 +10392,10 @@
         <v>60011</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10406,10 +10403,10 @@
         <v>60012</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10417,10 +10414,10 @@
         <v>60013</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10428,10 +10425,10 @@
         <v>60014</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10439,10 +10436,10 @@
         <v>60015</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10450,10 +10447,10 @@
         <v>60016</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10461,10 +10458,10 @@
         <v>60017</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10472,10 +10469,10 @@
         <v>60018</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10483,10 +10480,10 @@
         <v>60019</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10494,10 +10491,10 @@
         <v>60020</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10505,10 +10502,10 @@
         <v>60021</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10516,10 +10513,10 @@
         <v>60022</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10527,10 +10524,10 @@
         <v>60025</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10538,10 +10535,10 @@
         <v>60026</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10549,10 +10546,10 @@
         <v>60029</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10560,10 +10557,10 @@
         <v>60030</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10571,10 +10568,10 @@
         <v>60031</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10582,10 +10579,10 @@
         <v>60035</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10593,10 +10590,10 @@
         <v>60037</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10604,10 +10601,10 @@
         <v>60038</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10615,10 +10612,10 @@
         <v>60039</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10626,10 +10623,10 @@
         <v>60040</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10637,10 +10634,10 @@
         <v>60041</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10648,10 +10645,10 @@
         <v>60042</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10659,10 +10656,10 @@
         <v>60043</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10670,10 +10667,10 @@
         <v>60044</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10681,10 +10678,10 @@
         <v>60045</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10692,10 +10689,10 @@
         <v>60046</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10703,10 +10700,10 @@
         <v>60047</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10714,10 +10711,10 @@
         <v>60048</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10725,10 +10722,10 @@
         <v>60050</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10736,10 +10733,10 @@
         <v>60051</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10747,10 +10744,10 @@
         <v>60053</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10758,10 +10755,10 @@
         <v>60055</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10769,10 +10766,10 @@
         <v>60056</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10780,10 +10777,10 @@
         <v>60060</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10791,10 +10788,10 @@
         <v>60061</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10802,10 +10799,10 @@
         <v>60062</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10813,10 +10810,10 @@
         <v>60064</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10824,10 +10821,10 @@
         <v>60065</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10835,10 +10832,10 @@
         <v>60067</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10846,10 +10843,10 @@
         <v>60068</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10857,10 +10854,10 @@
         <v>60069</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10868,10 +10865,10 @@
         <v>60070</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10879,10 +10876,10 @@
         <v>60071</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10890,10 +10887,10 @@
         <v>60072</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10901,10 +10898,10 @@
         <v>60073</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10912,10 +10909,10 @@
         <v>60074</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10923,10 +10920,10 @@
         <v>60075</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10934,10 +10931,10 @@
         <v>60076</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10945,10 +10942,10 @@
         <v>60077</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10956,10 +10953,10 @@
         <v>60078</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10967,10 +10964,10 @@
         <v>60079</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10978,10 +10975,10 @@
         <v>60081</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10989,10 +10986,10 @@
         <v>60082</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11000,10 +10997,10 @@
         <v>60083</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11011,10 +11008,10 @@
         <v>60084</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11022,10 +11019,10 @@
         <v>60085</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11033,10 +11030,10 @@
         <v>60086</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11044,10 +11041,10 @@
         <v>60087</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11055,10 +11052,10 @@
         <v>60088</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11066,10 +11063,10 @@
         <v>60089</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11077,10 +11074,10 @@
         <v>60090</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11088,10 +11085,10 @@
         <v>60091</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C73" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11099,10 +11096,10 @@
         <v>60093</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11110,10 +11107,10 @@
         <v>60094</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11121,10 +11118,10 @@
         <v>60095</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11132,10 +11129,10 @@
         <v>60096</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11143,10 +11140,10 @@
         <v>60097</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11154,10 +11151,10 @@
         <v>60098</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11165,10 +11162,10 @@
         <v>60099</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11176,10 +11173,10 @@
         <v>60101</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11187,10 +11184,10 @@
         <v>60102</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11198,10 +11195,10 @@
         <v>60103</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11209,10 +11206,10 @@
         <v>60104</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11220,10 +11217,10 @@
         <v>60105</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11231,10 +11228,10 @@
         <v>60106</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11242,10 +11239,10 @@
         <v>60107</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11253,10 +11250,10 @@
         <v>60108</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11264,10 +11261,10 @@
         <v>60109</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11275,10 +11272,10 @@
         <v>60110</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11286,10 +11283,10 @@
         <v>60112</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11297,10 +11294,10 @@
         <v>60115</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11308,10 +11305,10 @@
         <v>60116</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C93" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11319,10 +11316,10 @@
         <v>60117</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11330,10 +11327,10 @@
         <v>60118</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11341,10 +11338,10 @@
         <v>60119</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11352,10 +11349,10 @@
         <v>60120</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C97" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11363,10 +11360,10 @@
         <v>60121</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11374,10 +11371,10 @@
         <v>60122</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C99" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11385,10 +11382,10 @@
         <v>60123</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C100" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11396,10 +11393,10 @@
         <v>60124</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C101" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11407,10 +11404,10 @@
         <v>60126</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11418,10 +11415,10 @@
         <v>60128</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C103" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11429,10 +11426,10 @@
         <v>60130</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C104" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11440,10 +11437,10 @@
         <v>60131</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C105" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11451,10 +11448,10 @@
         <v>60132</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C106" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11462,10 +11459,10 @@
         <v>60133</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C107" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11473,10 +11470,10 @@
         <v>60134</v>
       </c>
       <c r="B108" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C108" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11484,10 +11481,10 @@
         <v>60135</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C109" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11495,10 +11492,10 @@
         <v>60136</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C110" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11506,10 +11503,10 @@
         <v>60137</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C111" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11517,10 +11514,10 @@
         <v>60138</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C112" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11528,10 +11525,10 @@
         <v>60139</v>
       </c>
       <c r="B113" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C113" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11539,10 +11536,10 @@
         <v>60140</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C114" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11550,10 +11547,10 @@
         <v>60141</v>
       </c>
       <c r="B115" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C115" s="17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11561,10 +11558,10 @@
         <v>60142</v>
       </c>
       <c r="B116" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C116" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11572,10 +11569,10 @@
         <v>60143</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C117" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11583,10 +11580,10 @@
         <v>60144</v>
       </c>
       <c r="B118" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C118" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11594,10 +11591,10 @@
         <v>60147</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C119" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11605,10 +11602,10 @@
         <v>60148</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C120" s="17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11616,10 +11613,10 @@
         <v>60151</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C121" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11627,10 +11624,10 @@
         <v>60152</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C122" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11638,10 +11635,10 @@
         <v>60153</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C123" s="17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11649,10 +11646,10 @@
         <v>60154</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C124" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11660,10 +11657,10 @@
         <v>60155</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C125" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11671,10 +11668,10 @@
         <v>60156</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C126" s="17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11682,10 +11679,10 @@
         <v>60157</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C127" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11693,10 +11690,10 @@
         <v>60159</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C128" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11704,10 +11701,10 @@
         <v>60160</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C129" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11715,10 +11712,10 @@
         <v>60161</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C130" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11726,10 +11723,10 @@
         <v>60162</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C131" s="17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11737,10 +11734,10 @@
         <v>60163</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C132" s="17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11748,10 +11745,10 @@
         <v>60164</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C133" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11759,10 +11756,10 @@
         <v>60165</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C134" s="17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11770,10 +11767,10 @@
         <v>60168</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11781,10 +11778,10 @@
         <v>60169</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11792,10 +11789,10 @@
         <v>60171</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11803,10 +11800,10 @@
         <v>60172</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C138" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11814,10 +11811,10 @@
         <v>60173</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C139" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11825,10 +11822,10 @@
         <v>60174</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C140" s="17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11836,10 +11833,10 @@
         <v>60175</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C141" s="17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11847,10 +11844,10 @@
         <v>60176</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C142" s="17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11858,10 +11855,10 @@
         <v>60177</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11869,10 +11866,10 @@
         <v>60178</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11880,10 +11877,10 @@
         <v>60179</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11891,10 +11888,10 @@
         <v>60180</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C146" s="17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11902,10 +11899,10 @@
         <v>60181</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C147" s="17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11913,10 +11910,10 @@
         <v>60183</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C148" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11924,10 +11921,10 @@
         <v>60184</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C149" s="17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11935,10 +11932,10 @@
         <v>60185</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C150" s="17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11946,10 +11943,10 @@
         <v>60186</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C151" s="17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11957,10 +11954,10 @@
         <v>60187</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C152" s="17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11968,10 +11965,10 @@
         <v>60188</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C153" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11979,10 +11976,10 @@
         <v>60189</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C154" s="17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11990,10 +11987,10 @@
         <v>60190</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C155" s="17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12001,10 +11998,10 @@
         <v>60191</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C156" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12012,10 +12009,10 @@
         <v>60192</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C157" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12023,10 +12020,10 @@
         <v>60193</v>
       </c>
       <c r="B158" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C158" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12034,10 +12031,10 @@
         <v>60194</v>
       </c>
       <c r="B159" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C159" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12045,10 +12042,10 @@
         <v>60195</v>
       </c>
       <c r="B160" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C160" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12056,10 +12053,10 @@
         <v>60196</v>
       </c>
       <c r="B161" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C161" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12067,10 +12064,10 @@
         <v>60197</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C162" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12078,10 +12075,10 @@
         <v>60199</v>
       </c>
       <c r="B163" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C163" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12089,10 +12086,10 @@
         <v>60201</v>
       </c>
       <c r="B164" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C164" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12100,10 +12097,10 @@
         <v>60202</v>
       </c>
       <c r="B165" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C165" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12111,10 +12108,10 @@
         <v>60203</v>
       </c>
       <c r="B166" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C166" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12122,10 +12119,10 @@
         <v>60204</v>
       </c>
       <c r="B167" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C167" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12133,10 +12130,10 @@
         <v>60208</v>
       </c>
       <c r="B168" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C168" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12144,10 +12141,10 @@
         <v>60301</v>
       </c>
       <c r="B169" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C169" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12155,10 +12152,10 @@
         <v>60302</v>
       </c>
       <c r="B170" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C170" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12166,10 +12163,10 @@
         <v>60303</v>
       </c>
       <c r="B171" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C171" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12177,10 +12174,10 @@
         <v>60304</v>
       </c>
       <c r="B172" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C172" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12188,10 +12185,10 @@
         <v>60305</v>
       </c>
       <c r="B173" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C173" s="17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12199,10 +12196,10 @@
         <v>60399</v>
       </c>
       <c r="B174" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C174" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12210,10 +12207,10 @@
         <v>60402</v>
       </c>
       <c r="B175" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C175" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12221,10 +12218,10 @@
         <v>60403</v>
       </c>
       <c r="B176" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C176" s="17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12232,10 +12229,10 @@
         <v>60404</v>
       </c>
       <c r="B177" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C177" s="17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12243,10 +12240,10 @@
         <v>60406</v>
       </c>
       <c r="B178" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C178" s="17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12254,10 +12251,10 @@
         <v>60409</v>
       </c>
       <c r="B179" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C179" s="17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12265,10 +12262,10 @@
         <v>60410</v>
       </c>
       <c r="B180" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C180" s="17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12276,10 +12273,10 @@
         <v>60411</v>
       </c>
       <c r="B181" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C181" s="17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12287,10 +12284,10 @@
         <v>60412</v>
       </c>
       <c r="B182" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C182" s="17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12298,10 +12295,10 @@
         <v>60415</v>
       </c>
       <c r="B183" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C183" s="17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12309,10 +12306,10 @@
         <v>60418</v>
       </c>
       <c r="B184" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C184" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12320,10 +12317,10 @@
         <v>60419</v>
       </c>
       <c r="B185" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C185" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12331,10 +12328,10 @@
         <v>60421</v>
       </c>
       <c r="B186" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C186" s="17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12342,10 +12339,10 @@
         <v>60422</v>
       </c>
       <c r="B187" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C187" s="17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12353,10 +12350,10 @@
         <v>60423</v>
       </c>
       <c r="B188" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C188" s="17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12364,10 +12361,10 @@
         <v>60425</v>
       </c>
       <c r="B189" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C189" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12375,10 +12372,10 @@
         <v>60426</v>
       </c>
       <c r="B190" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C190" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12386,10 +12383,10 @@
         <v>60428</v>
       </c>
       <c r="B191" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C191" s="17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12397,10 +12394,10 @@
         <v>60429</v>
       </c>
       <c r="B192" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C192" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12408,10 +12405,10 @@
         <v>60430</v>
       </c>
       <c r="B193" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C193" s="17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12419,10 +12416,10 @@
         <v>60431</v>
       </c>
       <c r="B194" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C194" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12430,10 +12427,10 @@
         <v>60432</v>
       </c>
       <c r="B195" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C195" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12441,10 +12438,10 @@
         <v>60433</v>
       </c>
       <c r="B196" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C196" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12452,10 +12449,10 @@
         <v>60434</v>
       </c>
       <c r="B197" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C197" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12463,10 +12460,10 @@
         <v>60435</v>
       </c>
       <c r="B198" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C198" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12474,10 +12471,10 @@
         <v>60436</v>
       </c>
       <c r="B199" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C199" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12485,10 +12482,10 @@
         <v>60438</v>
       </c>
       <c r="B200" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C200" s="17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12496,10 +12493,10 @@
         <v>60439</v>
       </c>
       <c r="B201" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C201" s="17" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12507,10 +12504,10 @@
         <v>60440</v>
       </c>
       <c r="B202" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C202" s="17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12518,10 +12515,10 @@
         <v>60441</v>
       </c>
       <c r="B203" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C203" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12529,10 +12526,10 @@
         <v>60442</v>
       </c>
       <c r="B204" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C204" s="17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12540,10 +12537,10 @@
         <v>60443</v>
       </c>
       <c r="B205" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C205" s="17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12551,10 +12548,10 @@
         <v>60445</v>
       </c>
       <c r="B206" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C206" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12562,10 +12559,10 @@
         <v>60446</v>
       </c>
       <c r="B207" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C207" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12573,10 +12570,10 @@
         <v>60447</v>
       </c>
       <c r="B208" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C208" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12584,10 +12581,10 @@
         <v>60448</v>
       </c>
       <c r="B209" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C209" s="17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12595,10 +12592,10 @@
         <v>60449</v>
       </c>
       <c r="B210" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C210" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12606,10 +12603,10 @@
         <v>60451</v>
       </c>
       <c r="B211" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C211" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12617,10 +12614,10 @@
         <v>60452</v>
       </c>
       <c r="B212" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C212" s="17" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12628,10 +12625,10 @@
         <v>60453</v>
       </c>
       <c r="B213" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C213" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12639,10 +12636,10 @@
         <v>60454</v>
       </c>
       <c r="B214" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C214" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12650,10 +12647,10 @@
         <v>60455</v>
       </c>
       <c r="B215" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C215" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12661,10 +12658,10 @@
         <v>60456</v>
       </c>
       <c r="B216" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C216" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12672,10 +12669,10 @@
         <v>60457</v>
       </c>
       <c r="B217" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C217" s="17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12683,10 +12680,10 @@
         <v>60458</v>
       </c>
       <c r="B218" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C218" s="17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12694,10 +12691,10 @@
         <v>60459</v>
       </c>
       <c r="B219" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C219" s="17" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12705,10 +12702,10 @@
         <v>60461</v>
       </c>
       <c r="B220" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C220" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12716,10 +12713,10 @@
         <v>60462</v>
       </c>
       <c r="B221" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C221" s="17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12727,10 +12724,10 @@
         <v>60463</v>
       </c>
       <c r="B222" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C222" s="17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12738,10 +12735,10 @@
         <v>60464</v>
       </c>
       <c r="B223" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C223" s="17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12749,10 +12746,10 @@
         <v>60465</v>
       </c>
       <c r="B224" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C224" s="17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12760,10 +12757,10 @@
         <v>60466</v>
       </c>
       <c r="B225" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C225" s="17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12771,10 +12768,10 @@
         <v>60467</v>
       </c>
       <c r="B226" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C226" s="17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12782,10 +12779,10 @@
         <v>60469</v>
       </c>
       <c r="B227" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C227" s="17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12793,10 +12790,10 @@
         <v>60471</v>
       </c>
       <c r="B228" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C228" s="17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12804,10 +12801,10 @@
         <v>60472</v>
       </c>
       <c r="B229" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C229" s="17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12815,10 +12812,10 @@
         <v>60473</v>
       </c>
       <c r="B230" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C230" s="17" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12826,10 +12823,10 @@
         <v>60475</v>
       </c>
       <c r="B231" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C231" s="17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12837,10 +12834,10 @@
         <v>60476</v>
       </c>
       <c r="B232" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C232" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12848,10 +12845,10 @@
         <v>60477</v>
       </c>
       <c r="B233" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C233" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12859,10 +12856,10 @@
         <v>60478</v>
       </c>
       <c r="B234" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C234" s="17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12870,10 +12867,10 @@
         <v>60480</v>
       </c>
       <c r="B235" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C235" s="17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12881,10 +12878,10 @@
         <v>60482</v>
       </c>
       <c r="B236" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C236" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12892,10 +12889,10 @@
         <v>60484</v>
       </c>
       <c r="B237" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C237" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12903,10 +12900,10 @@
         <v>60487</v>
       </c>
       <c r="B238" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C238" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12914,10 +12911,10 @@
         <v>60490</v>
       </c>
       <c r="B239" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C239" s="17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12925,10 +12922,10 @@
         <v>60491</v>
       </c>
       <c r="B240" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C240" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12936,10 +12933,10 @@
         <v>60499</v>
       </c>
       <c r="B241" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C241" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12947,10 +12944,10 @@
         <v>60501</v>
       </c>
       <c r="B242" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C242" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12958,10 +12955,10 @@
         <v>60502</v>
       </c>
       <c r="B243" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C243" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12969,10 +12966,10 @@
         <v>60503</v>
       </c>
       <c r="B244" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C244" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12980,10 +12977,10 @@
         <v>60504</v>
       </c>
       <c r="B245" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C245" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12991,10 +12988,10 @@
         <v>60505</v>
       </c>
       <c r="B246" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C246" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13002,10 +12999,10 @@
         <v>60506</v>
       </c>
       <c r="B247" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C247" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13013,10 +13010,10 @@
         <v>60507</v>
       </c>
       <c r="B248" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C248" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13024,10 +13021,10 @@
         <v>60510</v>
       </c>
       <c r="B249" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C249" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13035,10 +13032,10 @@
         <v>60511</v>
       </c>
       <c r="B250" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C250" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13046,10 +13043,10 @@
         <v>60512</v>
       </c>
       <c r="B251" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C251" s="17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13057,10 +13054,10 @@
         <v>60513</v>
       </c>
       <c r="B252" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C252" s="17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13068,10 +13065,10 @@
         <v>60514</v>
       </c>
       <c r="B253" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C253" s="17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13079,10 +13076,10 @@
         <v>60515</v>
       </c>
       <c r="B254" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C254" s="17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13090,10 +13087,10 @@
         <v>60516</v>
       </c>
       <c r="B255" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C255" s="17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13101,10 +13098,10 @@
         <v>60517</v>
       </c>
       <c r="B256" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C256" s="17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13112,10 +13109,10 @@
         <v>60519</v>
       </c>
       <c r="B257" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C257" s="17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13123,10 +13120,10 @@
         <v>60520</v>
       </c>
       <c r="B258" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C258" s="17" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13134,10 +13131,10 @@
         <v>60521</v>
       </c>
       <c r="B259" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C259" s="17" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13145,10 +13142,10 @@
         <v>60522</v>
       </c>
       <c r="B260" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C260" s="17" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13156,10 +13153,10 @@
         <v>60523</v>
       </c>
       <c r="B261" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C261" s="17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13167,10 +13164,10 @@
         <v>60525</v>
       </c>
       <c r="B262" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C262" s="17" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13178,10 +13175,10 @@
         <v>60526</v>
       </c>
       <c r="B263" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C263" s="17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13189,10 +13186,10 @@
         <v>60527</v>
       </c>
       <c r="B264" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C264" s="17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13200,10 +13197,10 @@
         <v>60532</v>
       </c>
       <c r="B265" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C265" s="17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13211,10 +13208,10 @@
         <v>60534</v>
       </c>
       <c r="B266" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C266" s="17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13222,10 +13219,10 @@
         <v>60536</v>
       </c>
       <c r="B267" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C267" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13233,10 +13230,10 @@
         <v>60538</v>
       </c>
       <c r="B268" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C268" s="17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13244,10 +13241,10 @@
         <v>60539</v>
       </c>
       <c r="B269" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C269" s="17" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13255,10 +13252,10 @@
         <v>60540</v>
       </c>
       <c r="B270" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C270" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13266,10 +13263,10 @@
         <v>60541</v>
       </c>
       <c r="B271" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C271" s="17" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13277,10 +13274,10 @@
         <v>60542</v>
       </c>
       <c r="B272" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C272" s="17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13288,10 +13285,10 @@
         <v>60543</v>
       </c>
       <c r="B273" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C273" s="17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13299,10 +13296,10 @@
         <v>60544</v>
       </c>
       <c r="B274" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C274" s="17" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13310,10 +13307,10 @@
         <v>60545</v>
       </c>
       <c r="B275" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C275" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13321,10 +13318,10 @@
         <v>60546</v>
       </c>
       <c r="B276" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C276" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13332,10 +13329,10 @@
         <v>60548</v>
       </c>
       <c r="B277" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C277" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13343,10 +13340,10 @@
         <v>60554</v>
       </c>
       <c r="B278" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C278" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13354,10 +13351,10 @@
         <v>60555</v>
       </c>
       <c r="B279" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C279" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13365,10 +13362,10 @@
         <v>60558</v>
       </c>
       <c r="B280" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C280" s="17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13376,10 +13373,10 @@
         <v>60559</v>
       </c>
       <c r="B281" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C281" s="17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13387,10 +13384,10 @@
         <v>60560</v>
       </c>
       <c r="B282" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C282" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13398,10 +13395,10 @@
         <v>60561</v>
       </c>
       <c r="B283" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C283" s="17" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13409,10 +13406,10 @@
         <v>60563</v>
       </c>
       <c r="B284" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C284" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13420,10 +13417,10 @@
         <v>60564</v>
       </c>
       <c r="B285" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C285" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13431,10 +13428,10 @@
         <v>60565</v>
       </c>
       <c r="B286" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C286" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13442,10 +13439,10 @@
         <v>60566</v>
       </c>
       <c r="B287" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C287" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13453,10 +13450,10 @@
         <v>60567</v>
       </c>
       <c r="B288" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C288" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13464,10 +13461,10 @@
         <v>60568</v>
       </c>
       <c r="B289" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C289" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13475,10 +13472,10 @@
         <v>60569</v>
       </c>
       <c r="B290" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C290" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13486,10 +13483,10 @@
         <v>60572</v>
       </c>
       <c r="B291" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C291" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13497,10 +13494,10 @@
         <v>60585</v>
       </c>
       <c r="B292" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C292" s="17" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13508,10 +13505,10 @@
         <v>60586</v>
       </c>
       <c r="B293" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C293" s="17" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13519,10 +13516,10 @@
         <v>60598</v>
       </c>
       <c r="B294" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C294" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13530,10 +13527,10 @@
         <v>60599</v>
       </c>
       <c r="B295" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C295" s="17" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13541,10 +13538,10 @@
         <v>60607</v>
       </c>
       <c r="B296" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C296" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13552,10 +13549,10 @@
         <v>60608</v>
       </c>
       <c r="B297" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C297" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13563,10 +13560,10 @@
         <v>60609</v>
       </c>
       <c r="B298" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C298" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13574,10 +13571,10 @@
         <v>60612</v>
       </c>
       <c r="B299" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C299" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13585,10 +13582,10 @@
         <v>60613</v>
       </c>
       <c r="B300" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C300" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13596,10 +13593,10 @@
         <v>60614</v>
       </c>
       <c r="B301" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C301" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13607,10 +13604,10 @@
         <v>60615</v>
       </c>
       <c r="B302" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C302" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13618,10 +13615,10 @@
         <v>60616</v>
       </c>
       <c r="B303" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C303" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13629,10 +13626,10 @@
         <v>60617</v>
       </c>
       <c r="B304" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C304" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13640,10 +13637,10 @@
         <v>60618</v>
       </c>
       <c r="B305" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C305" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13651,10 +13648,10 @@
         <v>60619</v>
       </c>
       <c r="B306" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C306" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13662,10 +13659,10 @@
         <v>60620</v>
       </c>
       <c r="B307" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C307" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13673,10 +13670,10 @@
         <v>60621</v>
       </c>
       <c r="B308" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C308" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13684,10 +13681,10 @@
         <v>60622</v>
       </c>
       <c r="B309" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C309" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13695,10 +13692,10 @@
         <v>60623</v>
       </c>
       <c r="B310" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C310" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13706,10 +13703,10 @@
         <v>60624</v>
       </c>
       <c r="B311" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C311" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13717,10 +13714,10 @@
         <v>60625</v>
       </c>
       <c r="B312" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C312" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13728,10 +13725,10 @@
         <v>60626</v>
       </c>
       <c r="B313" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C313" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13739,10 +13736,10 @@
         <v>60628</v>
       </c>
       <c r="B314" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C314" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13750,10 +13747,10 @@
         <v>60629</v>
       </c>
       <c r="B315" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C315" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13761,10 +13758,10 @@
         <v>60630</v>
       </c>
       <c r="B316" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C316" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13772,10 +13769,10 @@
         <v>60631</v>
       </c>
       <c r="B317" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C317" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13783,10 +13780,10 @@
         <v>60632</v>
       </c>
       <c r="B318" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C318" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13794,10 +13791,10 @@
         <v>60633</v>
       </c>
       <c r="B319" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C319" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13805,10 +13802,10 @@
         <v>60634</v>
       </c>
       <c r="B320" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C320" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13816,10 +13813,10 @@
         <v>60636</v>
       </c>
       <c r="B321" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C321" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13827,10 +13824,10 @@
         <v>60637</v>
       </c>
       <c r="B322" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C322" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13838,10 +13835,10 @@
         <v>60638</v>
       </c>
       <c r="B323" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C323" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13849,10 +13846,10 @@
         <v>60639</v>
       </c>
       <c r="B324" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C324" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13860,10 +13857,10 @@
         <v>60640</v>
       </c>
       <c r="B325" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C325" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13871,10 +13868,10 @@
         <v>60641</v>
       </c>
       <c r="B326" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C326" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13882,10 +13879,10 @@
         <v>60643</v>
       </c>
       <c r="B327" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C327" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13893,10 +13890,10 @@
         <v>60644</v>
       </c>
       <c r="B328" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C328" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13904,10 +13901,10 @@
         <v>60645</v>
       </c>
       <c r="B329" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C329" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13915,10 +13912,10 @@
         <v>60646</v>
       </c>
       <c r="B330" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C330" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13926,10 +13923,10 @@
         <v>60647</v>
       </c>
       <c r="B331" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C331" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13937,10 +13934,10 @@
         <v>60649</v>
       </c>
       <c r="B332" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C332" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13948,10 +13945,10 @@
         <v>60651</v>
       </c>
       <c r="B333" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C333" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13959,10 +13956,10 @@
         <v>60652</v>
       </c>
       <c r="B334" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C334" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13970,10 +13967,10 @@
         <v>60653</v>
       </c>
       <c r="B335" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C335" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13981,10 +13978,10 @@
         <v>60655</v>
       </c>
       <c r="B336" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C336" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13992,10 +13989,10 @@
         <v>60656</v>
       </c>
       <c r="B337" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C337" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14003,10 +14000,10 @@
         <v>60657</v>
       </c>
       <c r="B338" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C338" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14014,10 +14011,10 @@
         <v>60659</v>
       </c>
       <c r="B339" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C339" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14025,10 +14022,10 @@
         <v>60660</v>
       </c>
       <c r="B340" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C340" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14036,10 +14033,10 @@
         <v>60664</v>
       </c>
       <c r="B341" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C341" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14047,10 +14044,10 @@
         <v>60666</v>
       </c>
       <c r="B342" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C342" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14058,10 +14055,10 @@
         <v>60668</v>
       </c>
       <c r="B343" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C343" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14069,10 +14066,10 @@
         <v>60669</v>
       </c>
       <c r="B344" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C344" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14080,10 +14077,10 @@
         <v>60670</v>
       </c>
       <c r="B345" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C345" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14091,10 +14088,10 @@
         <v>60673</v>
       </c>
       <c r="B346" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C346" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14102,10 +14099,10 @@
         <v>60674</v>
       </c>
       <c r="B347" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C347" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14113,10 +14110,10 @@
         <v>60675</v>
       </c>
       <c r="B348" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C348" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14124,10 +14121,10 @@
         <v>60677</v>
       </c>
       <c r="B349" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C349" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14135,10 +14132,10 @@
         <v>60678</v>
       </c>
       <c r="B350" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C350" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14146,10 +14143,10 @@
         <v>60680</v>
       </c>
       <c r="B351" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C351" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14157,10 +14154,10 @@
         <v>60681</v>
       </c>
       <c r="B352" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C352" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14168,10 +14165,10 @@
         <v>60682</v>
       </c>
       <c r="B353" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C353" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14179,10 +14176,10 @@
         <v>60684</v>
       </c>
       <c r="B354" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C354" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14190,10 +14187,10 @@
         <v>60685</v>
       </c>
       <c r="B355" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C355" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14201,10 +14198,10 @@
         <v>60686</v>
       </c>
       <c r="B356" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C356" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14212,10 +14209,10 @@
         <v>60687</v>
       </c>
       <c r="B357" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C357" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14223,10 +14220,10 @@
         <v>60688</v>
       </c>
       <c r="B358" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C358" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14234,10 +14231,10 @@
         <v>60689</v>
       </c>
       <c r="B359" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C359" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14245,10 +14242,10 @@
         <v>60690</v>
       </c>
       <c r="B360" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C360" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14256,10 +14253,10 @@
         <v>60691</v>
       </c>
       <c r="B361" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C361" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14267,10 +14264,10 @@
         <v>60693</v>
       </c>
       <c r="B362" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C362" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14278,10 +14275,10 @@
         <v>60694</v>
       </c>
       <c r="B363" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C363" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14289,10 +14286,10 @@
         <v>60695</v>
       </c>
       <c r="B364" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C364" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14300,10 +14297,10 @@
         <v>60696</v>
       </c>
       <c r="B365" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C365" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14311,10 +14308,10 @@
         <v>60697</v>
       </c>
       <c r="B366" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C366" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14322,10 +14319,10 @@
         <v>60699</v>
       </c>
       <c r="B367" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C367" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14333,10 +14330,10 @@
         <v>60701</v>
       </c>
       <c r="B368" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C368" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14344,10 +14341,10 @@
         <v>60706</v>
       </c>
       <c r="B369" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C369" s="17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14355,10 +14352,10 @@
         <v>60707</v>
       </c>
       <c r="B370" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C370" s="17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14366,10 +14363,10 @@
         <v>60712</v>
       </c>
       <c r="B371" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C371" s="17" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14377,10 +14374,10 @@
         <v>60714</v>
       </c>
       <c r="B372" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C372" s="17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14388,10 +14385,10 @@
         <v>60803</v>
       </c>
       <c r="B373" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C373" s="17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14399,10 +14396,10 @@
         <v>60804</v>
       </c>
       <c r="B374" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C374" s="17" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14410,10 +14407,10 @@
         <v>60805</v>
       </c>
       <c r="B375" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C375" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14421,10 +14418,10 @@
         <v>60827</v>
       </c>
       <c r="B376" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C376" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17566,7 +17563,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
